--- a/templates/ERC000033/metadata_template_ERC000033.xlsx
+++ b/templates/ERC000033/metadata_template_ERC000033.xlsx
@@ -25,7 +25,7 @@
     <definedName name="hosthabitat">'cv_sample'!$AI$1:$AI$7</definedName>
     <definedName name="hosthealthstate">'cv_sample'!$W$1:$W$14</definedName>
     <definedName name="hostsex">'cv_sample'!$X$1:$X$17</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$85</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="657">
   <si>
     <t>alias</t>
   </si>
@@ -562,6 +562,9 @@
     <t>DNBSEQ-G50</t>
   </si>
   <si>
+    <t>DNBSEQ-G800</t>
+  </si>
+  <si>
     <t>DNBSEQ-T10x4RS</t>
   </si>
   <si>
@@ -725,6 +728,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>Vega</t>
   </si>
   <si>
     <t>instrument_model</t>
@@ -2532,7 +2538,7 @@
         <v>143</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2576,7 +2582,7 @@
         <v>144</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2603,7 +2609,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N85"/>
+  <dimension ref="G1:N87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3322,6 +3328,16 @@
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="86" spans="14:14">
+      <c r="N86" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14">
+      <c r="N87" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3343,27 +3359,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3383,122 +3399,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3522,240 +3538,240 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="2" spans="1:40" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
   </sheetData>
@@ -3796,74 +3812,74 @@
   <sheetData>
     <row r="1" spans="9:39">
       <c r="I1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="R1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="S1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="W1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="X1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AI1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AM1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="2" spans="9:39">
       <c r="I2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="R2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="S2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="W2" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="X2" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AI2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="AM2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="3" spans="9:39">
       <c r="Q3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="R3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="S3" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="W3" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="X3" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AI3" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AM3" t="s">
         <v>116</v>
@@ -3871,22 +3887,22 @@
     </row>
     <row r="4" spans="9:39">
       <c r="Q4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="R4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="W4" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="X4" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AI4" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="AM4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="5" spans="9:39">
@@ -3894,13 +3910,13 @@
         <v>116</v>
       </c>
       <c r="R5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="W5" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="X5" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AI5" t="s">
         <v>116</v>
@@ -3908,126 +3924,126 @@
     </row>
     <row r="6" spans="9:39">
       <c r="Q6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="R6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="W6" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X6" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AI6" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="7" spans="9:39">
       <c r="Q7" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="R7" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="W7" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="X7" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AI7" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="8" spans="9:39">
       <c r="R8" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="W8" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="X8" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="9" spans="9:39">
       <c r="R9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="W9" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="X9" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="10" spans="9:39">
       <c r="R10" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="W10" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="X10" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="11" spans="9:39">
       <c r="R11" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="W11" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="X11" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="12" spans="9:39">
       <c r="R12" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="W12" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="X12" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="13" spans="9:39">
       <c r="R13" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="W13" t="s">
+        <v>591</v>
+      </c>
+      <c r="X13" t="s">
         <v>589</v>
-      </c>
-      <c r="X13" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="14" spans="9:39">
       <c r="R14" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="W14" t="s">
+        <v>592</v>
+      </c>
+      <c r="X14" t="s">
         <v>590</v>
-      </c>
-      <c r="X14" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="15" spans="9:39">
       <c r="R15" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="X15" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="16" spans="9:39">
       <c r="R16" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="X16" t="s">
         <v>116</v>
@@ -4035,1370 +4051,1370 @@
     </row>
     <row r="17" spans="18:24">
       <c r="R17" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="X17" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="18" spans="18:24">
       <c r="R18" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="19" spans="18:24">
       <c r="R19" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="20" spans="18:24">
       <c r="R20" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="21" spans="18:24">
       <c r="R21" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22" spans="18:24">
       <c r="R22" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="23" spans="18:24">
       <c r="R23" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="24" spans="18:24">
       <c r="R24" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="25" spans="18:24">
       <c r="R25" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="26" spans="18:24">
       <c r="R26" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="27" spans="18:24">
       <c r="R27" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="28" spans="18:24">
       <c r="R28" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="29" spans="18:24">
       <c r="R29" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="30" spans="18:24">
       <c r="R30" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="31" spans="18:24">
       <c r="R31" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="32" spans="18:24">
       <c r="R32" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="33" spans="18:18">
       <c r="R33" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="34" spans="18:18">
       <c r="R34" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="35" spans="18:18">
       <c r="R35" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="36" spans="18:18">
       <c r="R36" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37" spans="18:18">
       <c r="R37" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="38" spans="18:18">
       <c r="R38" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="39" spans="18:18">
       <c r="R39" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="40" spans="18:18">
       <c r="R40" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="41" spans="18:18">
       <c r="R41" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="42" spans="18:18">
       <c r="R42" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="43" spans="18:18">
       <c r="R43" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="44" spans="18:18">
       <c r="R44" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="45" spans="18:18">
       <c r="R45" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="46" spans="18:18">
       <c r="R46" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="47" spans="18:18">
       <c r="R47" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="48" spans="18:18">
       <c r="R48" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="49" spans="18:18">
       <c r="R49" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="50" spans="18:18">
       <c r="R50" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="51" spans="18:18">
       <c r="R51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="52" spans="18:18">
       <c r="R52" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="53" spans="18:18">
       <c r="R53" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="54" spans="18:18">
       <c r="R54" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="55" spans="18:18">
       <c r="R55" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="56" spans="18:18">
       <c r="R56" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="57" spans="18:18">
       <c r="R57" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="58" spans="18:18">
       <c r="R58" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="59" spans="18:18">
       <c r="R59" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="60" spans="18:18">
       <c r="R60" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="61" spans="18:18">
       <c r="R61" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="62" spans="18:18">
       <c r="R62" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="63" spans="18:18">
       <c r="R63" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="64" spans="18:18">
       <c r="R64" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="65" spans="18:18">
       <c r="R65" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="66" spans="18:18">
       <c r="R66" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="67" spans="18:18">
       <c r="R67" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="68" spans="18:18">
       <c r="R68" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="69" spans="18:18">
       <c r="R69" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="70" spans="18:18">
       <c r="R70" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="71" spans="18:18">
       <c r="R71" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="72" spans="18:18">
       <c r="R72" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="73" spans="18:18">
       <c r="R73" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="74" spans="18:18">
       <c r="R74" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="75" spans="18:18">
       <c r="R75" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="76" spans="18:18">
       <c r="R76" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="77" spans="18:18">
       <c r="R77" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="78" spans="18:18">
       <c r="R78" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="79" spans="18:18">
       <c r="R79" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="80" spans="18:18">
       <c r="R80" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="81" spans="18:18">
       <c r="R81" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="82" spans="18:18">
       <c r="R82" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="83" spans="18:18">
       <c r="R83" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="84" spans="18:18">
       <c r="R84" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="85" spans="18:18">
       <c r="R85" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="86" spans="18:18">
       <c r="R86" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="87" spans="18:18">
       <c r="R87" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="88" spans="18:18">
       <c r="R88" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="89" spans="18:18">
       <c r="R89" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="90" spans="18:18">
       <c r="R90" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="91" spans="18:18">
       <c r="R91" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="92" spans="18:18">
       <c r="R92" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="93" spans="18:18">
       <c r="R93" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="94" spans="18:18">
       <c r="R94" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="95" spans="18:18">
       <c r="R95" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="96" spans="18:18">
       <c r="R96" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="97" spans="18:18">
       <c r="R97" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="98" spans="18:18">
       <c r="R98" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="99" spans="18:18">
       <c r="R99" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="100" spans="18:18">
       <c r="R100" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="101" spans="18:18">
       <c r="R101" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="102" spans="18:18">
       <c r="R102" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="103" spans="18:18">
       <c r="R103" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="104" spans="18:18">
       <c r="R104" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="105" spans="18:18">
       <c r="R105" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="106" spans="18:18">
       <c r="R106" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="107" spans="18:18">
       <c r="R107" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="108" spans="18:18">
       <c r="R108" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="109" spans="18:18">
       <c r="R109" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="110" spans="18:18">
       <c r="R110" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="111" spans="18:18">
       <c r="R111" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="112" spans="18:18">
       <c r="R112" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="113" spans="18:18">
       <c r="R113" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="114" spans="18:18">
       <c r="R114" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="115" spans="18:18">
       <c r="R115" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="116" spans="18:18">
       <c r="R116" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="117" spans="18:18">
       <c r="R117" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="118" spans="18:18">
       <c r="R118" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="119" spans="18:18">
       <c r="R119" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="120" spans="18:18">
       <c r="R120" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="121" spans="18:18">
       <c r="R121" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="122" spans="18:18">
       <c r="R122" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="123" spans="18:18">
       <c r="R123" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="124" spans="18:18">
       <c r="R124" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="125" spans="18:18">
       <c r="R125" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="126" spans="18:18">
       <c r="R126" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="127" spans="18:18">
       <c r="R127" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="128" spans="18:18">
       <c r="R128" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="129" spans="18:18">
       <c r="R129" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="130" spans="18:18">
       <c r="R130" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="131" spans="18:18">
       <c r="R131" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="132" spans="18:18">
       <c r="R132" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="133" spans="18:18">
       <c r="R133" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="134" spans="18:18">
       <c r="R134" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="135" spans="18:18">
       <c r="R135" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="136" spans="18:18">
       <c r="R136" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="137" spans="18:18">
       <c r="R137" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="138" spans="18:18">
       <c r="R138" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="139" spans="18:18">
       <c r="R139" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="140" spans="18:18">
       <c r="R140" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="141" spans="18:18">
       <c r="R141" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="142" spans="18:18">
       <c r="R142" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="143" spans="18:18">
       <c r="R143" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="144" spans="18:18">
       <c r="R144" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="145" spans="18:18">
       <c r="R145" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="146" spans="18:18">
       <c r="R146" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="147" spans="18:18">
       <c r="R147" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="148" spans="18:18">
       <c r="R148" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="149" spans="18:18">
       <c r="R149" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="150" spans="18:18">
       <c r="R150" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="151" spans="18:18">
       <c r="R151" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="152" spans="18:18">
       <c r="R152" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="153" spans="18:18">
       <c r="R153" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="154" spans="18:18">
       <c r="R154" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="155" spans="18:18">
       <c r="R155" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="156" spans="18:18">
       <c r="R156" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="157" spans="18:18">
       <c r="R157" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="158" spans="18:18">
       <c r="R158" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="159" spans="18:18">
       <c r="R159" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="160" spans="18:18">
       <c r="R160" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="161" spans="18:18">
       <c r="R161" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="162" spans="18:18">
       <c r="R162" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="163" spans="18:18">
       <c r="R163" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="164" spans="18:18">
       <c r="R164" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="165" spans="18:18">
       <c r="R165" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="166" spans="18:18">
       <c r="R166" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="167" spans="18:18">
       <c r="R167" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="168" spans="18:18">
       <c r="R168" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="169" spans="18:18">
       <c r="R169" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="170" spans="18:18">
       <c r="R170" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="171" spans="18:18">
       <c r="R171" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="172" spans="18:18">
       <c r="R172" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="173" spans="18:18">
       <c r="R173" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="174" spans="18:18">
       <c r="R174" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="175" spans="18:18">
       <c r="R175" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="176" spans="18:18">
       <c r="R176" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="177" spans="18:18">
       <c r="R177" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="178" spans="18:18">
       <c r="R178" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="179" spans="18:18">
       <c r="R179" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="180" spans="18:18">
       <c r="R180" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="181" spans="18:18">
       <c r="R181" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="182" spans="18:18">
       <c r="R182" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="183" spans="18:18">
       <c r="R183" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="184" spans="18:18">
       <c r="R184" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="185" spans="18:18">
       <c r="R185" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="186" spans="18:18">
       <c r="R186" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="187" spans="18:18">
       <c r="R187" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="188" spans="18:18">
       <c r="R188" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="189" spans="18:18">
       <c r="R189" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="190" spans="18:18">
       <c r="R190" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="191" spans="18:18">
       <c r="R191" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="192" spans="18:18">
       <c r="R192" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="193" spans="18:18">
       <c r="R193" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="194" spans="18:18">
       <c r="R194" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="195" spans="18:18">
       <c r="R195" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="196" spans="18:18">
       <c r="R196" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="197" spans="18:18">
       <c r="R197" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="198" spans="18:18">
       <c r="R198" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="199" spans="18:18">
       <c r="R199" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="200" spans="18:18">
       <c r="R200" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="201" spans="18:18">
       <c r="R201" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="202" spans="18:18">
       <c r="R202" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="203" spans="18:18">
       <c r="R203" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="204" spans="18:18">
       <c r="R204" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="205" spans="18:18">
       <c r="R205" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="206" spans="18:18">
       <c r="R206" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="207" spans="18:18">
       <c r="R207" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="208" spans="18:18">
       <c r="R208" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="209" spans="18:18">
       <c r="R209" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="210" spans="18:18">
       <c r="R210" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="211" spans="18:18">
       <c r="R211" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="212" spans="18:18">
       <c r="R212" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="213" spans="18:18">
       <c r="R213" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="214" spans="18:18">
       <c r="R214" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="215" spans="18:18">
       <c r="R215" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="216" spans="18:18">
       <c r="R216" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="217" spans="18:18">
       <c r="R217" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="218" spans="18:18">
       <c r="R218" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="219" spans="18:18">
       <c r="R219" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="220" spans="18:18">
       <c r="R220" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="221" spans="18:18">
       <c r="R221" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="222" spans="18:18">
       <c r="R222" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="223" spans="18:18">
       <c r="R223" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="224" spans="18:18">
       <c r="R224" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="225" spans="18:18">
       <c r="R225" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="226" spans="18:18">
       <c r="R226" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="227" spans="18:18">
       <c r="R227" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="228" spans="18:18">
       <c r="R228" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="229" spans="18:18">
       <c r="R229" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="230" spans="18:18">
       <c r="R230" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="231" spans="18:18">
       <c r="R231" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="232" spans="18:18">
       <c r="R232" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="233" spans="18:18">
       <c r="R233" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="234" spans="18:18">
       <c r="R234" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="235" spans="18:18">
       <c r="R235" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="236" spans="18:18">
       <c r="R236" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="237" spans="18:18">
       <c r="R237" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="238" spans="18:18">
       <c r="R238" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="239" spans="18:18">
       <c r="R239" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="240" spans="18:18">
       <c r="R240" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="241" spans="18:18">
       <c r="R241" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="242" spans="18:18">
       <c r="R242" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="243" spans="18:18">
       <c r="R243" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="244" spans="18:18">
       <c r="R244" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="245" spans="18:18">
       <c r="R245" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="246" spans="18:18">
       <c r="R246" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="247" spans="18:18">
       <c r="R247" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="248" spans="18:18">
       <c r="R248" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="249" spans="18:18">
       <c r="R249" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="250" spans="18:18">
       <c r="R250" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="251" spans="18:18">
       <c r="R251" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="252" spans="18:18">
       <c r="R252" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="253" spans="18:18">
       <c r="R253" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="254" spans="18:18">
       <c r="R254" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="255" spans="18:18">
       <c r="R255" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="256" spans="18:18">
       <c r="R256" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="257" spans="18:18">
       <c r="R257" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="258" spans="18:18">
       <c r="R258" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="259" spans="18:18">
       <c r="R259" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="260" spans="18:18">
       <c r="R260" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="261" spans="18:18">
       <c r="R261" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="262" spans="18:18">
       <c r="R262" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="263" spans="18:18">
       <c r="R263" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="264" spans="18:18">
       <c r="R264" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="265" spans="18:18">
       <c r="R265" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="266" spans="18:18">
       <c r="R266" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="267" spans="18:18">
       <c r="R267" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="268" spans="18:18">
       <c r="R268" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="269" spans="18:18">
       <c r="R269" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="270" spans="18:18">
       <c r="R270" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="271" spans="18:18">
       <c r="R271" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="272" spans="18:18">
       <c r="R272" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="273" spans="18:18">
       <c r="R273" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="274" spans="18:18">
       <c r="R274" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="275" spans="18:18">
       <c r="R275" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="276" spans="18:18">
       <c r="R276" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="277" spans="18:18">
       <c r="R277" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="278" spans="18:18">
       <c r="R278" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="279" spans="18:18">
       <c r="R279" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="280" spans="18:18">
       <c r="R280" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="281" spans="18:18">
       <c r="R281" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="282" spans="18:18">
       <c r="R282" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="283" spans="18:18">
       <c r="R283" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="284" spans="18:18">
       <c r="R284" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="285" spans="18:18">
       <c r="R285" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="286" spans="18:18">
       <c r="R286" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="287" spans="18:18">
       <c r="R287" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="288" spans="18:18">
       <c r="R288" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="289" spans="18:18">
       <c r="R289" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000033/metadata_template_ERC000033.xlsx
+++ b/templates/ERC000033/metadata_template_ERC000033.xlsx
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$R$1:$R$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$R$1:$R$294</definedName>
     <definedName name="hospitalisation">'cv_sample'!$I$1:$I$2</definedName>
     <definedName name="hostbehaviour">'cv_sample'!$AM$1:$AM$4</definedName>
     <definedName name="hostdiseaseoutcome">'cv_sample'!$S$1:$S$3</definedName>
     <definedName name="hosthabitat">'cv_sample'!$AI$1:$AI$7</definedName>
     <definedName name="hosthealthstate">'cv_sample'!$W$1:$W$14</definedName>
     <definedName name="hostsex">'cv_sample'!$X$1:$X$17</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$86</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="662">
   <si>
     <t>alias</t>
   </si>
@@ -562,6 +562,9 @@
     <t>DNBSEQ-G50</t>
   </si>
   <si>
+    <t>DNBSEQ-G800</t>
+  </si>
+  <si>
     <t>DNBSEQ-T10x4RS</t>
   </si>
   <si>
@@ -847,25 +850,25 @@
     <t>(Optional) Free-form text describing the sample, its origin, and its method of isolation.</t>
   </si>
   <si>
-    <t>sample storage conditions</t>
+    <t>sample_storage_conditions</t>
   </si>
   <si>
     <t>(Optional) Conditions at which sample was stored, usually storage temperature, duration and location. in soil context: explain how and for how long the soil sample was stored before dna extraction (fresh/frozen/other).</t>
   </si>
   <si>
-    <t>subject exposure</t>
+    <t>subject_exposure</t>
   </si>
   <si>
     <t>(Optional) Exposure of the subject to infected human or animals, such as poultry, wild bird or swine. if multiple exposures are applicable, please state them separated by semicolon. example: poultry; wild bird</t>
   </si>
   <si>
-    <t>type exposure</t>
+    <t>type_exposure</t>
   </si>
   <si>
     <t>(Optional) Setting within which the subject is exposed to animals, such as farm, slaughterhouse, food preparation. if multiple exposures are applicable, please state their type in the same order in which you reported the exposure in the field 'subject exposure'. example: backyard flock; confined animal feeding operation</t>
   </si>
   <si>
-    <t>personal protective equipment</t>
+    <t>personal_protective_equipment</t>
   </si>
   <si>
     <t>(Optional) Use of personal protective equipment, such as gloves, gowns, during any type of exposure. example: mask</t>
@@ -883,46 +886,46 @@
     <t>(Optional) Was the subject confined to a hospital as a result of virus infection or problems occurring secondary to virus infection?</t>
   </si>
   <si>
-    <t>illness duration</t>
+    <t>illness_duration</t>
   </si>
   <si>
     <t>(Optional) The number of days the illness lasted. example: 4</t>
   </si>
   <si>
-    <t>illness symptoms</t>
+    <t>illness_symptoms</t>
   </si>
   <si>
     <t>(Optional) The symptoms that have been reported in relation to the illness, such as cough, diarrhea, fever, headache, malaise, myalgia, nausea, runny_nose, shortness_of_breath, sore_throat. if multiple exposures are applicable, please state them separated by semicolon.</t>
   </si>
   <si>
-    <t>collection date</t>
+    <t>collection_date</t>
   </si>
   <si>
     <t>(Mandatory) The date the sample was collected with the intention of sequencing, either as an instance (single point in time) or interval. in case no exact time is available, the date/time can be right truncated i.e. all of these are valid iso8601 compliant times: 2008-01-23t19:23:10+00:00; 2008-01-23t19:23:10; 2008-01-23; 2008-01; 2008.</t>
   </si>
   <si>
-    <t>geographic location (latitude)</t>
+    <t>geographic_location_latitude</t>
   </si>
   <si>
     <t>(Recommended) The geographical origin of the sample as defined by latitude. the values should be reported in decimal degrees and in wgs84 system (Units: DD)</t>
   </si>
   <si>
-    <t>geographic location (longitude)</t>
+    <t>geographic_location_longitude</t>
   </si>
   <si>
     <t>(Recommended) The geographical origin of the sample as defined by longitude. the values should be reported in decimal degrees and in wgs84 system (Units: DD)</t>
   </si>
   <si>
-    <t>geographic location (region and locality)</t>
+    <t>geographic_location_region_and_locality</t>
   </si>
   <si>
     <t>(Recommended) The geographical origin of the sample as defined by the specific region name followed by the locality name.</t>
   </si>
   <si>
-    <t>subject exposure duration</t>
-  </si>
-  <si>
-    <t>(Optional) Duration of the exposure of the subject to an infected human or animal. if multiple exposures are applicable, please state their duration in the same order in which you reported the exposure in the field 'subject exposure'. example: 1 day; 0.33 days (Units: year)</t>
+    <t>subject_exposure_duration</t>
+  </si>
+  <si>
+    <t>(Optional) Duration of the exposure of the subject to an infected human or animal. if multiple exposures are applicable, please state their duration in the same order in which you reported the exposure in the field 'subject exposure'. example: 1 day; 0.33 days (Units: day)</t>
   </si>
   <si>
     <t>active surveillance in response to outbreak</t>
@@ -943,7 +946,7 @@
     <t>zoo sample</t>
   </si>
   <si>
-    <t>sample capture status</t>
+    <t>sample_capture_status</t>
   </si>
   <si>
     <t>(Recommended) Reason for the sample collection.</t>
@@ -1162,9 +1165,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1183,6 +1183,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1384,6 +1387,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1393,9 +1399,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1435,7 +1438,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1504,6 +1507,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1579,6 +1585,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1600,6 +1609,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1645,6 +1657,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1657,6 +1672,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1666,9 +1684,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1693,6 +1708,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -1753,12 +1771,12 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
   </si>
   <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
     <t>Wallis and Futuna</t>
   </si>
   <si>
@@ -1816,7 +1834,7 @@
     <t>restricted access</t>
   </si>
   <si>
-    <t>geographic location (country and/or sea)</t>
+    <t>geographic_location_country_andor_sea</t>
   </si>
   <si>
     <t>(Mandatory) The geographical origin of where the sample was collected from, with the intention of sequencing, as defined by the country or sea name. country or sea names should be chosen from the insdc country list (http://insdc.org/country.html).</t>
@@ -1831,25 +1849,25 @@
     <t>recovered with sequelae</t>
   </si>
   <si>
-    <t>host disease outcome</t>
+    <t>host_disease_outcome</t>
   </si>
   <si>
     <t>(Recommended) Disease outcome in the host.</t>
   </si>
   <si>
-    <t>host common name</t>
+    <t>host_common_name</t>
   </si>
   <si>
     <t>(Mandatory) Common name of the host, e.g. human</t>
   </si>
   <si>
-    <t>host subject id</t>
+    <t>host_subject_id</t>
   </si>
   <si>
     <t>(Mandatory) A unique identifier by which each subject can be referred to, de-identified, e.g. #131</t>
   </si>
   <si>
-    <t>host age</t>
+    <t>host_age</t>
   </si>
   <si>
     <t>(Recommended) Age of host at the time of sampling; relevant scale depends on species and study, e.g. could be seconds for amoebae or centuries for trees (Units: years)</t>
@@ -1861,7 +1879,7 @@
     <t>healthy</t>
   </si>
   <si>
-    <t>host health state</t>
+    <t>host_health_state</t>
   </si>
   <si>
     <t>(Mandatory) Health status of the host at the time of sample collection.</t>
@@ -1879,7 +1897,7 @@
     <t>neuter</t>
   </si>
   <si>
-    <t>host sex</t>
+    <t>host_sex</t>
   </si>
   <si>
     <t>(Mandatory) Gender or sex of the host.</t>
@@ -1891,43 +1909,43 @@
     <t>(Optional) Scientific name of the laboratory host used to propagate the source organism from which the sample was obtained</t>
   </si>
   <si>
-    <t>host scientific name</t>
+    <t>host_scientific_name</t>
   </si>
   <si>
     <t>(Mandatory) Scientific name of the natural (as opposed to laboratory) host to the organism from which sample was obtained.</t>
   </si>
   <si>
-    <t>virus identifier</t>
+    <t>virus_identifier</t>
   </si>
   <si>
     <t>(Recommended) Unique laboratory identifier assigned to the virus by the investigator. strain name is not sufficient since it might not be unique due to various passsages of the same virus. format: up to 50 alphanumeric characters</t>
   </si>
   <si>
-    <t>collector name</t>
+    <t>collector_name</t>
   </si>
   <si>
     <t>(Mandatory) Name of the person who collected the specimen. example: john smith</t>
   </si>
   <si>
-    <t>collecting institution</t>
+    <t>collecting_institution</t>
   </si>
   <si>
     <t>(Mandatory) Name of the institution to which the person collecting the specimen belongs. format: institute name, institute address</t>
   </si>
   <si>
-    <t>receipt date</t>
+    <t>receipt_date</t>
   </si>
   <si>
     <t>(Recommended) Date on which the sample was received. format:yyyy-mm-dd. please provide the highest precision possible. if the sample was received by the institution and not collected, the 'receipt date' must be provided instead. either the 'collection date' or 'receipt date' must be provided. if available, provide both dates.</t>
   </si>
   <si>
-    <t>definition for seropositive sample</t>
+    <t>definition_for_seropositive_sample</t>
   </si>
   <si>
     <t>(Recommended) The cut off value used by an investigatior in determining that a sample was seropositive.</t>
   </si>
   <si>
-    <t>serotype (required for a seropositive sample)</t>
+    <t>serotype_required_for_a_seropositive_sample</t>
   </si>
   <si>
     <t>(Recommended) Serological variety of a species characterised by its antigenic properties. for influenza, ha subtype should be the letter h followed by a number between 1-16 unless novel subtype is identified and the na subtype should be the letter n followed by a number between 1-9 unless novel subtype is identified. if only one of the subtypes have been tested then use the format h5nx or hxn1. example: h1n1</t>
@@ -1963,19 +1981,19 @@
     <t>wild:resident</t>
   </si>
   <si>
-    <t>host habitat</t>
+    <t>host_habitat</t>
   </si>
   <si>
     <t>(Recommended) Natural habitat of the avian or mammalian host.</t>
   </si>
   <si>
-    <t>isolation source host-associated</t>
+    <t>isolation_source_hostassociated</t>
   </si>
   <si>
     <t>(Recommended) Name of host tissue or organ sampled for analysis. example: tracheal tissue</t>
   </si>
   <si>
-    <t>host description</t>
+    <t>host_description</t>
   </si>
   <si>
     <t>(Optional) Other descriptive information relating to the host.</t>
@@ -1996,13 +2014,13 @@
     <t>wild</t>
   </si>
   <si>
-    <t>host behaviour</t>
+    <t>host_behaviour</t>
   </si>
   <si>
     <t>(Recommended) Natural behaviour of the host.</t>
   </si>
   <si>
-    <t>isolation source non-host-associated</t>
+    <t>isolation_source_nonhostassociated</t>
   </si>
   <si>
     <t>(Recommended) Describes the physical, environmental and/or local geographical source of the biological sample from which the sample was derived. example: soil</t>
@@ -2535,7 +2553,7 @@
         <v>143</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2579,7 +2597,7 @@
         <v>144</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2606,7 +2624,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N86"/>
+  <dimension ref="G1:N87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3330,6 +3348,11 @@
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14">
+      <c r="N87" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3351,27 +3374,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3391,122 +3414,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3530,240 +3553,240 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
     </row>
     <row r="2" spans="1:40" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
     </row>
   </sheetData>
@@ -3799,79 +3822,79 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="I1:AM289"/>
+  <dimension ref="I1:AM294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="9:39">
       <c r="I1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="R1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="S1" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="W1" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="X1" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="AI1" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="AM1" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
     </row>
     <row r="2" spans="9:39">
       <c r="I2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="R2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="S2" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="W2" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="X2" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="AI2" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="AM2" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
     </row>
     <row r="3" spans="9:39">
       <c r="Q3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="R3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="S3" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="W3" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="X3" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="AI3" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="AM3" t="s">
         <v>116</v>
@@ -3879,22 +3902,22 @@
     </row>
     <row r="4" spans="9:39">
       <c r="Q4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="R4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="W4" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="X4" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="AI4" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="AM4" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
     </row>
     <row r="5" spans="9:39">
@@ -3902,13 +3925,13 @@
         <v>116</v>
       </c>
       <c r="R5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="W5" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="X5" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="AI5" t="s">
         <v>116</v>
@@ -3916,126 +3939,126 @@
     </row>
     <row r="6" spans="9:39">
       <c r="Q6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="R6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="W6" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="X6" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="AI6" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
     </row>
     <row r="7" spans="9:39">
       <c r="Q7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="R7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="W7" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="X7" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="AI7" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
     </row>
     <row r="8" spans="9:39">
       <c r="R8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="W8" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="X8" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
     </row>
     <row r="9" spans="9:39">
       <c r="R9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="W9" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="X9" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
     </row>
     <row r="10" spans="9:39">
       <c r="R10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="W10" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="X10" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="11" spans="9:39">
       <c r="R11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="W11" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="X11" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
     </row>
     <row r="12" spans="9:39">
       <c r="R12" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="W12" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="X12" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
     </row>
     <row r="13" spans="9:39">
       <c r="R13" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="W13" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="X13" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
     </row>
     <row r="14" spans="9:39">
       <c r="R14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="W14" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="X14" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
     </row>
     <row r="15" spans="9:39">
       <c r="R15" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="X15" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
     </row>
     <row r="16" spans="9:39">
       <c r="R16" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="X16" t="s">
         <v>116</v>
@@ -4043,1370 +4066,1395 @@
     </row>
     <row r="17" spans="18:24">
       <c r="R17" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="X17" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
     </row>
     <row r="18" spans="18:24">
       <c r="R18" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="19" spans="18:24">
       <c r="R19" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="20" spans="18:24">
       <c r="R20" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="21" spans="18:24">
       <c r="R21" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22" spans="18:24">
       <c r="R22" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="23" spans="18:24">
       <c r="R23" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="24" spans="18:24">
       <c r="R24" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="25" spans="18:24">
       <c r="R25" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="26" spans="18:24">
       <c r="R26" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="27" spans="18:24">
       <c r="R27" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="28" spans="18:24">
       <c r="R28" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="29" spans="18:24">
       <c r="R29" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="30" spans="18:24">
       <c r="R30" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="31" spans="18:24">
       <c r="R31" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="32" spans="18:24">
       <c r="R32" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="33" spans="18:18">
       <c r="R33" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="34" spans="18:18">
       <c r="R34" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="35" spans="18:18">
       <c r="R35" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="36" spans="18:18">
       <c r="R36" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37" spans="18:18">
       <c r="R37" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="38" spans="18:18">
       <c r="R38" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="39" spans="18:18">
       <c r="R39" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="40" spans="18:18">
       <c r="R40" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="41" spans="18:18">
       <c r="R41" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="42" spans="18:18">
       <c r="R42" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="43" spans="18:18">
       <c r="R43" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="44" spans="18:18">
       <c r="R44" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="45" spans="18:18">
       <c r="R45" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="46" spans="18:18">
       <c r="R46" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="47" spans="18:18">
       <c r="R47" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="48" spans="18:18">
       <c r="R48" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="49" spans="18:18">
       <c r="R49" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="50" spans="18:18">
       <c r="R50" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="51" spans="18:18">
       <c r="R51" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="52" spans="18:18">
       <c r="R52" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="53" spans="18:18">
       <c r="R53" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="54" spans="18:18">
       <c r="R54" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="55" spans="18:18">
       <c r="R55" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="56" spans="18:18">
       <c r="R56" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="57" spans="18:18">
       <c r="R57" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="58" spans="18:18">
       <c r="R58" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="59" spans="18:18">
       <c r="R59" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="60" spans="18:18">
       <c r="R60" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="61" spans="18:18">
       <c r="R61" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="62" spans="18:18">
       <c r="R62" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="63" spans="18:18">
       <c r="R63" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="64" spans="18:18">
       <c r="R64" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="65" spans="18:18">
       <c r="R65" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="66" spans="18:18">
       <c r="R66" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="67" spans="18:18">
       <c r="R67" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="68" spans="18:18">
       <c r="R68" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="69" spans="18:18">
       <c r="R69" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="70" spans="18:18">
       <c r="R70" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="71" spans="18:18">
       <c r="R71" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="72" spans="18:18">
       <c r="R72" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="73" spans="18:18">
       <c r="R73" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="74" spans="18:18">
       <c r="R74" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="75" spans="18:18">
       <c r="R75" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="76" spans="18:18">
       <c r="R76" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="77" spans="18:18">
       <c r="R77" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="78" spans="18:18">
       <c r="R78" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="79" spans="18:18">
       <c r="R79" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="80" spans="18:18">
       <c r="R80" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="81" spans="18:18">
       <c r="R81" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="82" spans="18:18">
       <c r="R82" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="83" spans="18:18">
       <c r="R83" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="84" spans="18:18">
       <c r="R84" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="85" spans="18:18">
       <c r="R85" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="86" spans="18:18">
       <c r="R86" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="87" spans="18:18">
       <c r="R87" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="88" spans="18:18">
       <c r="R88" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="89" spans="18:18">
       <c r="R89" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="90" spans="18:18">
       <c r="R90" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="91" spans="18:18">
       <c r="R91" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="92" spans="18:18">
       <c r="R92" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="93" spans="18:18">
       <c r="R93" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="94" spans="18:18">
       <c r="R94" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="95" spans="18:18">
       <c r="R95" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="96" spans="18:18">
       <c r="R96" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="97" spans="18:18">
       <c r="R97" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="98" spans="18:18">
       <c r="R98" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="99" spans="18:18">
       <c r="R99" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="100" spans="18:18">
       <c r="R100" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="101" spans="18:18">
       <c r="R101" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="102" spans="18:18">
       <c r="R102" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="103" spans="18:18">
       <c r="R103" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="104" spans="18:18">
       <c r="R104" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="105" spans="18:18">
       <c r="R105" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="106" spans="18:18">
       <c r="R106" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="107" spans="18:18">
       <c r="R107" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="108" spans="18:18">
       <c r="R108" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="109" spans="18:18">
       <c r="R109" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="110" spans="18:18">
       <c r="R110" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="111" spans="18:18">
       <c r="R111" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="112" spans="18:18">
       <c r="R112" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="113" spans="18:18">
       <c r="R113" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="114" spans="18:18">
       <c r="R114" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="115" spans="18:18">
       <c r="R115" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="116" spans="18:18">
       <c r="R116" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="117" spans="18:18">
       <c r="R117" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="118" spans="18:18">
       <c r="R118" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="119" spans="18:18">
       <c r="R119" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="120" spans="18:18">
       <c r="R120" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="121" spans="18:18">
       <c r="R121" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="122" spans="18:18">
       <c r="R122" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="123" spans="18:18">
       <c r="R123" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="124" spans="18:18">
       <c r="R124" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="125" spans="18:18">
       <c r="R125" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="126" spans="18:18">
       <c r="R126" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="127" spans="18:18">
       <c r="R127" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="128" spans="18:18">
       <c r="R128" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="129" spans="18:18">
       <c r="R129" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="130" spans="18:18">
       <c r="R130" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="131" spans="18:18">
       <c r="R131" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="132" spans="18:18">
       <c r="R132" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="133" spans="18:18">
       <c r="R133" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="134" spans="18:18">
       <c r="R134" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="135" spans="18:18">
       <c r="R135" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="136" spans="18:18">
       <c r="R136" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="137" spans="18:18">
       <c r="R137" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="138" spans="18:18">
       <c r="R138" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="139" spans="18:18">
       <c r="R139" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="140" spans="18:18">
       <c r="R140" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="141" spans="18:18">
       <c r="R141" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="142" spans="18:18">
       <c r="R142" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="143" spans="18:18">
       <c r="R143" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="144" spans="18:18">
       <c r="R144" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="145" spans="18:18">
       <c r="R145" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="146" spans="18:18">
       <c r="R146" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="147" spans="18:18">
       <c r="R147" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="148" spans="18:18">
       <c r="R148" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="149" spans="18:18">
       <c r="R149" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="150" spans="18:18">
       <c r="R150" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="151" spans="18:18">
       <c r="R151" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="152" spans="18:18">
       <c r="R152" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="153" spans="18:18">
       <c r="R153" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="154" spans="18:18">
       <c r="R154" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="155" spans="18:18">
       <c r="R155" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="156" spans="18:18">
       <c r="R156" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="157" spans="18:18">
       <c r="R157" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="158" spans="18:18">
       <c r="R158" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="159" spans="18:18">
       <c r="R159" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="160" spans="18:18">
       <c r="R160" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="161" spans="18:18">
       <c r="R161" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="162" spans="18:18">
       <c r="R162" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="163" spans="18:18">
       <c r="R163" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="164" spans="18:18">
       <c r="R164" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="165" spans="18:18">
       <c r="R165" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="166" spans="18:18">
       <c r="R166" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="167" spans="18:18">
       <c r="R167" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="168" spans="18:18">
       <c r="R168" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="169" spans="18:18">
       <c r="R169" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="170" spans="18:18">
       <c r="R170" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="171" spans="18:18">
       <c r="R171" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="172" spans="18:18">
       <c r="R172" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="173" spans="18:18">
       <c r="R173" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="174" spans="18:18">
       <c r="R174" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="175" spans="18:18">
       <c r="R175" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="176" spans="18:18">
       <c r="R176" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="177" spans="18:18">
       <c r="R177" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="178" spans="18:18">
       <c r="R178" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="179" spans="18:18">
       <c r="R179" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="180" spans="18:18">
       <c r="R180" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="181" spans="18:18">
       <c r="R181" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="182" spans="18:18">
       <c r="R182" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="183" spans="18:18">
       <c r="R183" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="184" spans="18:18">
       <c r="R184" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="185" spans="18:18">
       <c r="R185" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="186" spans="18:18">
       <c r="R186" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="187" spans="18:18">
       <c r="R187" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="188" spans="18:18">
       <c r="R188" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="189" spans="18:18">
       <c r="R189" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="190" spans="18:18">
       <c r="R190" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="191" spans="18:18">
       <c r="R191" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="192" spans="18:18">
       <c r="R192" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="193" spans="18:18">
       <c r="R193" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="194" spans="18:18">
       <c r="R194" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="195" spans="18:18">
       <c r="R195" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="196" spans="18:18">
       <c r="R196" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="197" spans="18:18">
       <c r="R197" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="198" spans="18:18">
       <c r="R198" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="199" spans="18:18">
       <c r="R199" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="200" spans="18:18">
       <c r="R200" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="201" spans="18:18">
       <c r="R201" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="202" spans="18:18">
       <c r="R202" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="203" spans="18:18">
       <c r="R203" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="204" spans="18:18">
       <c r="R204" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="205" spans="18:18">
       <c r="R205" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="206" spans="18:18">
       <c r="R206" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="207" spans="18:18">
       <c r="R207" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="208" spans="18:18">
       <c r="R208" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="209" spans="18:18">
       <c r="R209" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="210" spans="18:18">
       <c r="R210" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="211" spans="18:18">
       <c r="R211" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="212" spans="18:18">
       <c r="R212" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="213" spans="18:18">
       <c r="R213" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="214" spans="18:18">
       <c r="R214" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="215" spans="18:18">
       <c r="R215" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="216" spans="18:18">
       <c r="R216" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="217" spans="18:18">
       <c r="R217" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="218" spans="18:18">
       <c r="R218" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="219" spans="18:18">
       <c r="R219" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="220" spans="18:18">
       <c r="R220" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="221" spans="18:18">
       <c r="R221" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="222" spans="18:18">
       <c r="R222" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="223" spans="18:18">
       <c r="R223" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="224" spans="18:18">
       <c r="R224" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="225" spans="18:18">
       <c r="R225" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="226" spans="18:18">
       <c r="R226" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="227" spans="18:18">
       <c r="R227" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="228" spans="18:18">
       <c r="R228" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="229" spans="18:18">
       <c r="R229" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="230" spans="18:18">
       <c r="R230" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="231" spans="18:18">
       <c r="R231" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="232" spans="18:18">
       <c r="R232" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="233" spans="18:18">
       <c r="R233" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="234" spans="18:18">
       <c r="R234" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="235" spans="18:18">
       <c r="R235" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="236" spans="18:18">
       <c r="R236" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="237" spans="18:18">
       <c r="R237" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="238" spans="18:18">
       <c r="R238" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="239" spans="18:18">
       <c r="R239" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="240" spans="18:18">
       <c r="R240" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="241" spans="18:18">
       <c r="R241" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="242" spans="18:18">
       <c r="R242" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="243" spans="18:18">
       <c r="R243" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="244" spans="18:18">
       <c r="R244" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="245" spans="18:18">
       <c r="R245" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="246" spans="18:18">
       <c r="R246" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="247" spans="18:18">
       <c r="R247" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="248" spans="18:18">
       <c r="R248" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="249" spans="18:18">
       <c r="R249" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="250" spans="18:18">
       <c r="R250" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="251" spans="18:18">
       <c r="R251" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="252" spans="18:18">
       <c r="R252" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="253" spans="18:18">
       <c r="R253" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="254" spans="18:18">
       <c r="R254" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="255" spans="18:18">
       <c r="R255" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="256" spans="18:18">
       <c r="R256" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="257" spans="18:18">
       <c r="R257" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="258" spans="18:18">
       <c r="R258" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="259" spans="18:18">
       <c r="R259" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="260" spans="18:18">
       <c r="R260" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="261" spans="18:18">
       <c r="R261" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="262" spans="18:18">
       <c r="R262" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="263" spans="18:18">
       <c r="R263" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="264" spans="18:18">
       <c r="R264" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="265" spans="18:18">
       <c r="R265" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="266" spans="18:18">
       <c r="R266" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="267" spans="18:18">
       <c r="R267" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="268" spans="18:18">
       <c r="R268" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="269" spans="18:18">
       <c r="R269" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="270" spans="18:18">
       <c r="R270" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="271" spans="18:18">
       <c r="R271" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="272" spans="18:18">
       <c r="R272" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="273" spans="18:18">
       <c r="R273" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="274" spans="18:18">
       <c r="R274" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="275" spans="18:18">
       <c r="R275" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="276" spans="18:18">
       <c r="R276" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="277" spans="18:18">
       <c r="R277" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="278" spans="18:18">
       <c r="R278" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="279" spans="18:18">
       <c r="R279" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="280" spans="18:18">
       <c r="R280" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="281" spans="18:18">
       <c r="R281" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="282" spans="18:18">
       <c r="R282" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="283" spans="18:18">
       <c r="R283" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="284" spans="18:18">
       <c r="R284" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="285" spans="18:18">
       <c r="R285" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="286" spans="18:18">
       <c r="R286" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="287" spans="18:18">
       <c r="R287" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="288" spans="18:18">
       <c r="R288" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="289" spans="18:18">
       <c r="R289" t="s">
-        <v>591</v>
+        <v>592</v>
+      </c>
+    </row>
+    <row r="290" spans="18:18">
+      <c r="R290" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="291" spans="18:18">
+      <c r="R291" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="292" spans="18:18">
+      <c r="R292" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="293" spans="18:18">
+      <c r="R293" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="294" spans="18:18">
+      <c r="R294" t="s">
+        <v>597</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000033/metadata_template_ERC000033.xlsx
+++ b/templates/ERC000033/metadata_template_ERC000033.xlsx
@@ -943,7 +943,7 @@
     <t>subject exposure duration</t>
   </si>
   <si>
-    <t>(Optional) Duration of the exposure of the subject to an infected human or animal. if multiple exposures are applicable, please state their duration in the same order in which you reported the exposure in the field 'subject exposure'. example: 1 day; 0.33 days (Units: year)</t>
+    <t>(Optional) Duration of the exposure of the subject to an infected human or animal. if multiple exposures are applicable, please state their duration in the same order in which you reported the exposure in the field 'subject exposure'. example: 1 day; 0.33 days (Units: day)</t>
   </si>
   <si>
     <t>active surveillance in response to outbreak</t>
